--- a/Plotting/result_data_long.xlsx
+++ b/Plotting/result_data_long.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M129"/>
+  <dimension ref="A1:M126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -631,32 +631,32 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Z:\AdOpt_NET0\AdOpt_results\MY\EmissionScope Greenfield\Chemelot\20250414173206_2030_minC_DD10-1\optimization_results.h5</t>
+          <t>Z:\AdOpt_NET0\AdOpt_results\MY\EmissionScope Greenfield\Chemelot\20250824144120_2030_minC_DD10-1\optimization_results.h5</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Z:\AdOpt_NET0\AdOpt_results\MY\EmissionScope Greenfield\Chemelot\20250503162304_2040_minC_DD10-1\optimization_results.h5</t>
+          <t>Z:\AdOpt_NET0\AdOpt_results\MY\EmissionScope Greenfield\Chemelot\20250904001209_2040_minC_DD10-1\optimization_results.h5</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Z:\AdOpt_NET0\AdOpt_results\MY\EmissionScope Greenfield\Chemelot\20250422092243_2050_minC_DD10-1\optimization_results.h5</t>
+          <t>Z:\AdOpt_NET0\AdOpt_results\MY\EmissionScope Greenfield\Chemelot\20250825173312_2050_minC_DD10-1\optimization_results.h5</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Z:\AdOpt_NET0\AdOpt_results\MY\EmissionScope Brownfield\Chemelot\20250423110222_2030_minC_DD10-1\optimization_results.h5</t>
+          <t>Z:\AdOpt_NET0\AdOpt_results\MY\EmissionScope Brownfield\Chemelot\20250826012905_2030_minC_DD10-1\optimization_results.h5</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Z:\AdOpt_NET0\AdOpt_results\MY\EmissionScope Brownfield\Chemelot\20250423162730_2040_minC_DD10-1\optimization_results.h5</t>
+          <t>Z:\AdOpt_NET0\AdOpt_results\MY\EmissionScope Brownfield\Chemelot\20250902115535_2040_minC_DD10-1\optimization_results.h5</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Z:\AdOpt_NET0\AdOpt_results\MY\EmissionScope Brownfield\Chemelot\20250426164252_2050_minC_DD10-1\optimization_results.h5</t>
+          <t>Z:\AdOpt_NET0\AdOpt_results\MY\EmissionScope Brownfield\Chemelot\20250912214813_2050_minC_DD10-1\optimization_results.h5</t>
         </is>
       </c>
     </row>
@@ -685,22 +685,22 @@
         <v>3077616961.227675</v>
       </c>
       <c r="H6" t="n">
-        <v>4335623617.181549</v>
+        <v>4331783582.488637</v>
       </c>
       <c r="I6" t="n">
-        <v>3690001250.370417</v>
+        <v>3715829196.992819</v>
       </c>
       <c r="J6" t="n">
-        <v>4145601469.212524</v>
+        <v>3957215719.347853</v>
       </c>
       <c r="K6" t="n">
-        <v>4234459195.868593</v>
+        <v>4204404416.871889</v>
       </c>
       <c r="L6" t="n">
-        <v>4034789598.546146</v>
+        <v>4155467800.729961</v>
       </c>
       <c r="M6" t="n">
-        <v>3957807264.45573</v>
+        <v>3848931541.717194</v>
       </c>
     </row>
     <row r="7">
@@ -724,10 +724,10 @@
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
-        <v>18701073.99577388</v>
+        <v>100246341.7625979</v>
       </c>
       <c r="M7" t="n">
-        <v>520583364.3133165</v>
+        <v>644484773.1825584</v>
       </c>
     </row>
     <row r="8">
@@ -752,13 +752,13 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="n">
-        <v>4234459195.868593</v>
+        <v>4204404416.871889</v>
       </c>
       <c r="L8" t="n">
-        <v>4053490672.54192</v>
+        <v>4255714142.492559</v>
       </c>
       <c r="M8" t="n">
-        <v>4478390628.769047</v>
+        <v>4493416314.899753</v>
       </c>
     </row>
     <row r="9">
@@ -782,18 +782,18 @@
         <v>122193903039.2201</v>
       </c>
       <c r="H9" t="n">
-        <v>130068708515.4465</v>
+        <v>129953507474.6591</v>
       </c>
       <c r="I9" t="n">
-        <v>110700037511.1125</v>
+        <v>111474875909.7846</v>
       </c>
       <c r="J9" t="n">
-        <v>124368044076.3757</v>
+        <v>118716471580.4356</v>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
-        <v>127476394231.8379</v>
+        <v>128532885325.016</v>
       </c>
     </row>
     <row r="10">
@@ -821,19 +821,19 @@
         <v>-6.984919309616089e-10</v>
       </c>
       <c r="H10" t="n">
-        <v>1585314.601209711</v>
+        <v>1562794.17534808</v>
       </c>
       <c r="I10" t="n">
-        <v>1062757.667</v>
+        <v>780220.7344999724</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>2125515.334001312</v>
+        <v>1560441.469210454</v>
       </c>
       <c r="L10" t="n">
-        <v>925980.2200084254</v>
+        <v>694002.7533077486</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -864,22 +864,22 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>282.6796352668781</v>
+        <v>277.7359905283249</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>1277.301659373517</v>
+        <v>1277.461432225463</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>197.6931760046769</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1026.498066774457</v>
+        <v>895.1924071126524</v>
       </c>
     </row>
     <row r="12">
@@ -907,22 +907,22 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>29.36413807663639</v>
+        <v>29.37843757033182</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1025670297845189</v>
+        <v>0.1002776786203548</v>
       </c>
       <c r="J12" t="n">
-        <v>27.92665043793396</v>
+        <v>27.92410714285498</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>28.25175</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>27.92581366160655</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -953,19 +953,19 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>83.53193656506618</v>
+        <v>122.628782443452</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>41.59677723356639</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>0.6831233139696922</v>
       </c>
       <c r="M13" t="n">
-        <v>362.924775899478</v>
+        <v>425.1001219329846</v>
       </c>
     </row>
     <row r="14">
@@ -993,19 +993,19 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>2.397682768479084</v>
+        <v>2.377286868723894</v>
       </c>
       <c r="I14" t="n">
-        <v>26.65051462965602</v>
+        <v>27.68892338833814</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>44.30601663477577</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>413.1272700336363</v>
+        <v>334.423240750184</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1039,19 +1039,19 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>53.98765915183444</v>
+        <v>89.15494377446952</v>
       </c>
       <c r="J15" t="n">
-        <v>55.67753542372878</v>
+        <v>46.53619481845088</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>63.76725947358676</v>
+        <v>30.55614792408207</v>
       </c>
       <c r="M15" t="n">
-        <v>58.91407355860478</v>
+        <v>47.50766525741004</v>
       </c>
     </row>
     <row r="16">
@@ -1088,7 +1088,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>6.522996057621048</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -1116,10 +1116,10 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>496.8094804010865</v>
+        <v>496.809480401133</v>
       </c>
       <c r="I17" t="n">
-        <v>295.8387604708937</v>
+        <v>307.4889192285747</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1150,7 +1150,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>0.8705270331219307</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1190,7 +1190,7 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>480.8519360653743</v>
+        <v>374.6590730566556</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1270,22 +1270,22 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>718.4745866438434</v>
+        <v>722.2661971481764</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1031.562923132014</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>784.3100652934529</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>616.6657224618498</v>
       </c>
     </row>
     <row r="22">
@@ -1313,22 +1313,22 @@
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>845.0111676729897</v>
+        <v>845.4226638943688</v>
       </c>
       <c r="I22" t="n">
-        <v>2.951569202479543</v>
+        <v>2.885688593532714</v>
       </c>
       <c r="J22" t="n">
-        <v>803.644616919011</v>
+        <v>803.5714285722519</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>813</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>803.6205370246488</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1356,13 +1356,13 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>845.0111676729897</v>
+        <v>845.4226638943688</v>
       </c>
       <c r="I23" t="n">
-        <v>806.3173074331638</v>
+        <v>806.3227005647985</v>
       </c>
       <c r="J23" t="n">
-        <v>803.644616919011</v>
+        <v>803.5714285714139</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -1411,7 +1411,7 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>25.16773570882305</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -1454,7 +1454,7 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>0.8325719781061071</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -1491,16 +1491,16 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>158.758565432776</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>16.15068032936597</v>
+        <v>36.99657149196989</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>178.6150032193589</v>
       </c>
     </row>
     <row r="27">
@@ -1534,16 +1534,16 @@
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>192.9022666254872</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>19.62415592875574</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>261.9824723102417</v>
       </c>
     </row>
     <row r="28">
@@ -1565,13 +1565,13 @@
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
-        <v>496.8094804011101</v>
+        <v>496.8094804010362</v>
       </c>
       <c r="I28" t="n">
-        <v>295.8387604708937</v>
+        <v>307.4889192285747</v>
       </c>
       <c r="J28" t="n">
-        <v>480.851936065374</v>
+        <v>374.6590730566556</v>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
@@ -1608,16 +1608,16 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>4.385344546514462e-11</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>139.4422956017326</v>
+        <v>148.8846645451514</v>
       </c>
       <c r="M29" t="n">
-        <v>62.22827334226069</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -1700,7 +1700,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>23.11443572291606</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -1728,7 +1728,7 @@
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>1055.671140907662</v>
+        <v>1055.764798911148</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1759,7 +1759,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>0.7307625331623093</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1793,19 +1793,19 @@
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>8031.220348630261</v>
+        <v>8110.970291517405</v>
       </c>
       <c r="I34" t="n">
-        <v>1396.31660880907</v>
+        <v>1395.25812422677</v>
       </c>
       <c r="J34" t="n">
-        <v>76.10909367582423</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>28.51199999999994</v>
+        <v>4483.466879917355</v>
       </c>
       <c r="L34" t="n">
-        <v>1128.663540338653</v>
+        <v>4413.734581328684</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
@@ -1836,19 +1836,19 @@
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>1338.884284164562</v>
+        <v>1336.75920265175</v>
       </c>
       <c r="I35" t="n">
-        <v>4489.028038262079</v>
+        <v>4797.935867734877</v>
       </c>
       <c r="J35" t="n">
-        <v>-9.620954020219218e-12</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>751.9801491116556</v>
+        <v>1724.264985910204</v>
       </c>
       <c r="L35" t="n">
-        <v>4350.515467440772</v>
+        <v>6408.242743658212</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
@@ -1882,16 +1882,16 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>41.16020129801905</v>
+        <v>1055.598650361785</v>
       </c>
       <c r="J36" t="n">
-        <v>-8.964411993122974e-11</v>
+        <v>1.171035833635869e-06</v>
       </c>
       <c r="K36" t="n">
-        <v>6.654402102528422</v>
+        <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>4817.099911685627</v>
+        <v>2109.787796600112</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -1922,19 +1922,19 @@
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>2.335980298084905e-10</v>
       </c>
       <c r="I37" t="n">
-        <v>500</v>
+        <v>3307.369470726623</v>
       </c>
       <c r="J37" t="n">
-        <v>79.52372235661126</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>6.728399999930161</v>
+        <v>8.650800000310369</v>
       </c>
       <c r="L37" t="n">
-        <v>500</v>
+        <v>497.1776857096805</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
@@ -1965,19 +1965,19 @@
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>124.6378783694997</v>
+        <v>128.5339399073547</v>
       </c>
       <c r="I38" t="n">
-        <v>0.5026247359710713</v>
+        <v>0.5771377187601446</v>
       </c>
       <c r="J38" t="n">
-        <v>-1.1032238324706e-10</v>
+        <v>3.357172317919321e-10</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>238.1536521674365</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>410.7591208376246</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
@@ -2008,19 +2008,19 @@
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>-1.380371576296933e-10</v>
       </c>
       <c r="I39" t="n">
-        <v>8735.663655805742</v>
+        <v>5690.570831071151</v>
       </c>
       <c r="J39" t="n">
-        <v>130.6922726624625</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>5.767199999987153</v>
+        <v>8.650800000053652</v>
       </c>
       <c r="L39" t="n">
-        <v>9251.587161827001</v>
+        <v>9218.718177754034</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>134.3547477023987</v>
+        <v>135.063778866709</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
@@ -2060,7 +2060,7 @@
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>146.6659822098757</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -2094,22 +2094,22 @@
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>725.4745866438434</v>
+        <v>729.2661971481764</v>
       </c>
       <c r="I41" t="n">
-        <v>1089.321655537319</v>
+        <v>1090.453722299486</v>
       </c>
       <c r="J41" t="n">
-        <v>7</v>
+        <v>1038.562923131373</v>
       </c>
       <c r="K41" t="n">
-        <v>1119.63715986734</v>
+        <v>791.3100652934529</v>
       </c>
       <c r="L41" t="n">
-        <v>413.1272700336604</v>
+        <v>320.4071186734096</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>296.2586037884402</v>
       </c>
     </row>
     <row r="42">
@@ -2180,13 +2180,13 @@
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>3.871036824421026e-11</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>192.9022666256865</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -2195,7 +2195,7 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>261.9824723102416</v>
       </c>
     </row>
     <row r="44">
@@ -2266,7 +2266,7 @@
         <v>148</v>
       </c>
       <c r="H45" t="n">
-        <v>100.700063275586</v>
+        <v>101.4636898444023</v>
       </c>
       <c r="I45" t="n">
         <v>114</v>
@@ -2275,10 +2275,10 @@
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>114</v>
+        <v>113.9592628400361</v>
       </c>
       <c r="L45" t="n">
-        <v>82.93318857778478</v>
+        <v>113.9592628400362</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -2315,7 +2315,7 @@
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>55.67753543597797</v>
+        <v>46.53619560639657</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -2324,7 +2324,7 @@
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>122.6813330321915</v>
+        <v>78.06381318149211</v>
       </c>
     </row>
     <row r="47">
@@ -2567,7 +2567,7 @@
         <v>338</v>
       </c>
       <c r="H52" t="n">
-        <v>0</v>
+        <v>2.167253949998983e-11</v>
       </c>
       <c r="I52" t="n">
         <v>0</v>
@@ -2579,7 +2579,7 @@
         <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>25.16773570882305</v>
       </c>
       <c r="M52" t="n">
         <v>0</v>
@@ -2868,13 +2868,13 @@
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>91.22068676723228</v>
+        <v>89.72443846521497</v>
       </c>
       <c r="I59" t="n">
         <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>372.1453988827569</v>
+        <v>5.684341886080801e-14</v>
       </c>
       <c r="K59" t="n">
         <v>0</v>
@@ -2911,13 +2911,13 @@
         <v>2500.000000001289</v>
       </c>
       <c r="H60" t="n">
-        <v>750</v>
+        <v>750.0000000000758</v>
       </c>
       <c r="I60" t="n">
         <v>2000</v>
       </c>
       <c r="J60" t="n">
-        <v>2500.000000007237</v>
+        <v>2500.000000101131</v>
       </c>
       <c r="K60" t="n">
         <v>750</v>
@@ -2926,7 +2926,7 @@
         <v>2000</v>
       </c>
       <c r="M60" t="n">
-        <v>2500.000000007921</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="61">
@@ -3298,22 +3298,22 @@
         <v>44.69727137654262</v>
       </c>
       <c r="H69" t="n">
-        <v>46.07678054854758</v>
+        <v>45.27096645611697</v>
       </c>
       <c r="I69" t="n">
         <v>0</v>
       </c>
       <c r="J69" t="n">
-        <v>208.200170478013</v>
+        <v>208.2262135499708</v>
       </c>
       <c r="K69" t="n">
-        <v>0</v>
+        <v>32.22398768876234</v>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>6.444797537752461</v>
       </c>
       <c r="M69" t="n">
-        <v>167.3191848842364</v>
+        <v>178.1403500481247</v>
       </c>
     </row>
     <row r="70">
@@ -3427,22 +3427,22 @@
         <v>757.2247802366086</v>
       </c>
       <c r="H72" t="n">
-        <v>337.4663824510857</v>
+        <v>341.2579929569933</v>
       </c>
       <c r="I72" t="n">
-        <v>858.271583609551</v>
+        <v>850.3048763819691</v>
       </c>
       <c r="J72" t="n">
-        <v>3.600036815699374</v>
+        <v>745.9541870977073</v>
       </c>
       <c r="K72" t="n">
-        <v>733.9114905600854</v>
+        <v>421.077015293453</v>
       </c>
       <c r="L72" t="n">
-        <v>1532.764429901001</v>
+        <v>1111.717183966863</v>
       </c>
       <c r="M72" t="n">
-        <v>7</v>
+        <v>1407.975787755303</v>
       </c>
     </row>
     <row r="73">
@@ -3685,13 +3685,13 @@
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>496.8094804014871</v>
+        <v>496.8094804040155</v>
       </c>
       <c r="I78" t="n">
-        <v>295.8387604708937</v>
+        <v>307.4889192285747</v>
       </c>
       <c r="J78" t="n">
-        <v>480.8519360653744</v>
+        <v>374.6590730815856</v>
       </c>
       <c r="K78" t="n">
         <v>499</v>
@@ -3900,10 +3900,10 @@
         <v>0</v>
       </c>
       <c r="H83" t="n">
-        <v>0</v>
+        <v>4.000355602329364e-12</v>
       </c>
       <c r="I83" t="n">
-        <v>0.3282144953105938</v>
+        <v>0.2989773171691995</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -4072,22 +4072,22 @@
         <v>75.52313918315859</v>
       </c>
       <c r="H87" t="n">
-        <v>78.14906307484014</v>
+        <v>77.43000548752059</v>
       </c>
       <c r="I87" t="n">
-        <v>0.1258497455519617</v>
+        <v>0.1230407116761904</v>
       </c>
       <c r="J87" t="n">
-        <v>224.5839473341176</v>
+        <v>224.6046329547491</v>
       </c>
       <c r="K87" t="n">
-        <v>0</v>
+        <v>64.12118047469693</v>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>40.55615389493937</v>
       </c>
       <c r="M87" t="n">
-        <v>187.2131853144176</v>
+        <v>197.1028313487677</v>
       </c>
     </row>
     <row r="88">
@@ -4121,16 +4121,16 @@
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>0</v>
+        <v>1.403310254884628e-10</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
       </c>
       <c r="L88" t="n">
-        <v>139.4422956022084</v>
+        <v>148.8846645451514</v>
       </c>
       <c r="M88" t="n">
-        <v>201.6705689439933</v>
+        <v>148.8846645451514</v>
       </c>
     </row>
     <row r="89">
@@ -4330,16 +4330,16 @@
         <v>0</v>
       </c>
       <c r="H93" t="n">
-        <v>55.59289572185796</v>
+        <v>55.63980629162195</v>
       </c>
       <c r="I93" t="n">
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>115.6580831321342</v>
+        <v>1.678007777172752e-08</v>
       </c>
       <c r="K93" t="n">
-        <v>0</v>
+        <v>53.80990000000001</v>
       </c>
       <c r="L93" t="n">
         <v>0</v>
@@ -4542,14 +4542,14 @@
       </c>
       <c r="H98" t="inlineStr"/>
       <c r="I98" t="n">
-        <v>155.3457474964666</v>
+        <v>151.8783470212423</v>
       </c>
       <c r="J98" t="n">
-        <v>11.67753542373834</v>
+        <v>2.536194818450877</v>
       </c>
       <c r="K98" t="inlineStr"/>
       <c r="L98" t="n">
-        <v>161.3511675354761</v>
+        <v>138.8288494570355</v>
       </c>
       <c r="M98" t="n">
         <v>0</v>
@@ -4714,14 +4714,10 @@
       <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="n">
-        <v>1078</v>
-      </c>
-      <c r="L104" t="n">
-        <v>1078</v>
-      </c>
-      <c r="M104" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
@@ -4743,12 +4739,8 @@
       <c r="K105" t="n">
         <v>0</v>
       </c>
-      <c r="L105" t="n">
-        <v>0.8799542698396018</v>
-      </c>
-      <c r="M105" t="n">
-        <v>0</v>
-      </c>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
@@ -4770,8 +4762,12 @@
       <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr"/>
+      <c r="L106" t="n">
+        <v>197.6931760046769</v>
+      </c>
+      <c r="M106" t="n">
+        <v>197.6931760046769</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
@@ -4793,8 +4789,12 @@
       <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr"/>
+      <c r="L107" t="n">
+        <v>28.25175</v>
+      </c>
+      <c r="M107" t="n">
+        <v>28.25175</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
@@ -4816,11 +4816,9 @@
       <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr"/>
-      <c r="L108" t="n">
-        <v>41.59677723356639</v>
-      </c>
+      <c r="L108" t="inlineStr"/>
       <c r="M108" t="n">
-        <v>41.59677723356639</v>
+        <v>0.6831233139696922</v>
       </c>
     </row>
     <row r="109">
@@ -4843,11 +4841,9 @@
       <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr"/>
-      <c r="L109" t="n">
-        <v>44.30601663477577</v>
-      </c>
+      <c r="L109" t="inlineStr"/>
       <c r="M109" t="n">
-        <v>457.4332866684121</v>
+        <v>334.423240750184</v>
       </c>
     </row>
     <row r="110">
@@ -4870,8 +4866,12 @@
       <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr"/>
+      <c r="L110" t="n">
+        <v>784.3100652934529</v>
+      </c>
+      <c r="M110" t="n">
+        <v>784.3100652934529</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
@@ -4893,8 +4893,12 @@
       <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr"/>
+      <c r="L111" t="n">
+        <v>813</v>
+      </c>
+      <c r="M111" t="n">
+        <v>813</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
@@ -4917,7 +4921,9 @@
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr"/>
       <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr"/>
+      <c r="M112" t="n">
+        <v>25.16773570882305</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
@@ -4940,7 +4946,9 @@
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr"/>
       <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr"/>
+      <c r="M113" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
@@ -4964,7 +4972,7 @@
       <c r="K114" t="inlineStr"/>
       <c r="L114" t="inlineStr"/>
       <c r="M114" t="n">
-        <v>16.15068032936597</v>
+        <v>36.99657149196989</v>
       </c>
     </row>
     <row r="115">
@@ -4989,7 +4997,7 @@
       <c r="K115" t="inlineStr"/>
       <c r="L115" t="inlineStr"/>
       <c r="M115" t="n">
-        <v>139.4422956017326</v>
+        <v>148.8846645451514</v>
       </c>
     </row>
     <row r="116">
@@ -5040,10 +5048,10 @@
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr"/>
       <c r="L117" t="n">
-        <v>28.51199999999994</v>
+        <v>4483.466879917355</v>
       </c>
       <c r="M117" t="n">
-        <v>1157.175540338653</v>
+        <v>8897.201461246039</v>
       </c>
     </row>
     <row r="118">
@@ -5067,10 +5075,10 @@
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr"/>
       <c r="L118" t="n">
-        <v>751.9801491116556</v>
+        <v>1724.264985910204</v>
       </c>
       <c r="M118" t="n">
-        <v>5102.495616552428</v>
+        <v>8132.507729568416</v>
       </c>
     </row>
     <row r="119">
@@ -5093,8 +5101,12 @@
       <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr"/>
+      <c r="L119" t="n">
+        <v>238.1536521674365</v>
+      </c>
+      <c r="M119" t="n">
+        <v>648.9127730050611</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
@@ -5116,8 +5128,12 @@
       <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr"/>
-      <c r="L120" t="inlineStr"/>
-      <c r="M120" t="inlineStr"/>
+      <c r="L120" t="n">
+        <v>146.6659822098757</v>
+      </c>
+      <c r="M120" t="n">
+        <v>146.6659822098757</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
@@ -5140,10 +5156,10 @@
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr"/>
       <c r="L121" t="n">
-        <v>1119.63715986734</v>
+        <v>791.3100652934529</v>
       </c>
       <c r="M121" t="n">
-        <v>1532.764429901001</v>
+        <v>1111.717183966862</v>
       </c>
     </row>
     <row r="122">
@@ -5166,7 +5182,7 @@
       <c r="K122" t="inlineStr"/>
       <c r="L122" t="inlineStr"/>
       <c r="M122" t="n">
-        <v>63.76725947358676</v>
+        <v>30.55614792408207</v>
       </c>
     </row>
     <row r="123">
@@ -5189,7 +5205,7 @@
       <c r="K123" t="inlineStr"/>
       <c r="L123" t="inlineStr"/>
       <c r="M123" t="n">
-        <v>161.3511675354761</v>
+        <v>138.8288494570355</v>
       </c>
     </row>
     <row r="124">
@@ -5210,11 +5226,9 @@
       <c r="I124" t="inlineStr"/>
       <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr"/>
-      <c r="L124" t="n">
-        <v>6.654402102528422</v>
-      </c>
+      <c r="L124" t="inlineStr"/>
       <c r="M124" t="n">
-        <v>4823.754313788156</v>
+        <v>2109.787796600112</v>
       </c>
     </row>
     <row r="125">
@@ -5236,10 +5250,10 @@
       <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr"/>
       <c r="L125" t="n">
-        <v>6.728399999930161</v>
+        <v>8.650800000310369</v>
       </c>
       <c r="M125" t="n">
-        <v>506.7283999999302</v>
+        <v>505.8284857099908</v>
       </c>
     </row>
     <row r="126">
@@ -5261,75 +5275,10 @@
       <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr"/>
       <c r="L126" t="n">
-        <v>5.767199999987153</v>
+        <v>8.650800000053652</v>
       </c>
       <c r="M126" t="n">
-        <v>9257.354361826989</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="1" t="inlineStr">
-        <is>
-          <t>size_CO2toEmission_existing</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr"/>
-      <c r="C127" t="inlineStr"/>
-      <c r="D127" t="inlineStr"/>
-      <c r="E127" t="inlineStr"/>
-      <c r="F127" t="inlineStr"/>
-      <c r="G127" t="inlineStr"/>
-      <c r="H127" t="inlineStr"/>
-      <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
-      <c r="K127" t="inlineStr"/>
-      <c r="L127" t="n">
-        <v>6.522996057621048</v>
-      </c>
-      <c r="M127" t="n">
-        <v>6.522996057621048</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="1" t="inlineStr">
-        <is>
-          <t>size_MeOHsynthesis_existing</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr"/>
-      <c r="C128" t="inlineStr"/>
-      <c r="D128" t="inlineStr"/>
-      <c r="E128" t="inlineStr"/>
-      <c r="F128" t="inlineStr"/>
-      <c r="G128" t="inlineStr"/>
-      <c r="H128" t="inlineStr"/>
-      <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
-      <c r="L128" t="inlineStr"/>
-      <c r="M128" t="n">
-        <v>19.62415592875574</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="1" t="inlineStr">
-        <is>
-          <t>size_RWGS_existing</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr"/>
-      <c r="C129" t="inlineStr"/>
-      <c r="D129" t="inlineStr"/>
-      <c r="E129" t="inlineStr"/>
-      <c r="F129" t="inlineStr"/>
-      <c r="G129" t="inlineStr"/>
-      <c r="H129" t="inlineStr"/>
-      <c r="I129" t="inlineStr"/>
-      <c r="J129" t="inlineStr"/>
-      <c r="K129" t="inlineStr"/>
-      <c r="L129" t="inlineStr"/>
-      <c r="M129" t="n">
-        <v>23.11443572291606</v>
+        <v>9227.368977754088</v>
       </c>
     </row>
   </sheetData>
